--- a/01-projetos/01-data-project-foundations/data/input/absenteeism_data_21.xlsx
+++ b/01-projetos/01-data-project-foundations/data/input/absenteeism_data_21.xlsx
@@ -471,16 +471,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>36607</v>
+        <v>55948</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kamilly Castro</t>
+          <t>Theo da Cruz</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Jurídico</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -489,56 +489,56 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45082</v>
+        <v>45092</v>
       </c>
       <c r="G2" t="n">
-        <v>11486.06</v>
+        <v>3836.29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16474</v>
+        <v>47772</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Luiz Otávio Rezende</t>
+          <t>Maria Luiza Pereira</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Operações</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45090</v>
+        <v>45091</v>
       </c>
       <c r="G3" t="n">
-        <v>4713.18</v>
+        <v>5084.35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>72947</v>
+        <v>1314</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Leandro Melo</t>
+          <t>Joana da Mota</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -547,216 +547,216 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45089</v>
+        <v>45086</v>
       </c>
       <c r="G4" t="n">
-        <v>10347.02</v>
+        <v>6909.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1439</v>
+        <v>66671</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dra. Cecília Vieira</t>
+          <t>Bernardo Moraes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jurídico</t>
+          <t>Vendas</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45091</v>
+        <v>45088</v>
       </c>
       <c r="G5" t="n">
-        <v>7226.64</v>
+        <v>11849.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>50039</v>
+        <v>41626</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vicente Nogueira</t>
+          <t>Luiz Gustavo Viana</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atendimento ao Cliente</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45085</v>
+        <v>45091</v>
       </c>
       <c r="G6" t="n">
-        <v>8179.12</v>
+        <v>8807.860000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3724</v>
+        <v>82792</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Thomas Silveira</t>
+          <t>Paulo Vieira</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>Atendimento ao Cliente</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45083</v>
+        <v>45091</v>
       </c>
       <c r="G7" t="n">
-        <v>11965.59</v>
+        <v>3157.96</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>52327</v>
+        <v>69758</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Benjamin Azevedo</t>
+          <t>Clarice Moreira</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Consulta médica</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45088</v>
+        <v>45092</v>
       </c>
       <c r="G8" t="n">
-        <v>11136.73</v>
+        <v>5801.57</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>11949</v>
+        <v>93662</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dra. Maria Cecília Fogaça</t>
+          <t>Sophie Barros</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>P&amp;D</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Consulta médica</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>8</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45100</v>
+        <v>45093</v>
       </c>
       <c r="G9" t="n">
-        <v>4875.27</v>
+        <v>3857.93</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>91664</v>
+        <v>22915</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ana Lívia Mendes</t>
+          <t>Rodrigo da Mota</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>Jurídico</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Consulta médica</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45103</v>
+        <v>45088</v>
       </c>
       <c r="G10" t="n">
-        <v>12312.63</v>
+        <v>5091.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>52374</v>
+        <v>27029</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Brenda Santos</t>
+          <t>Sabrina Oliveira</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Jurídico</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Consulta médica</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>2</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45092</v>
+        <v>45085</v>
       </c>
       <c r="G11" t="n">
-        <v>4716.82</v>
+        <v>7428.08</v>
       </c>
     </row>
   </sheetData>
